--- a/materialy/zestawy-bez-ceny.xlsx
+++ b/materialy/zestawy-bez-ceny.xlsx
@@ -847,7 +847,11 @@
       <c r="E10" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -886,7 +890,11 @@
       <c r="E11" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1030,7 +1038,11 @@
       <c r="E15" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1069,7 +1081,11 @@
       <c r="E16" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1108,7 +1124,11 @@
       <c r="E17" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1225,7 +1245,11 @@
       <c r="E20" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1307,7 +1331,11 @@
       <c r="E22" s="5" t="n">
         <v>312</v>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1389,7 +1417,11 @@
       <c r="E24" s="5" t="n">
         <v>251</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1428,7 +1460,11 @@
       <c r="E25" s="10" t="n">
         <v>288</v>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1467,7 +1503,11 @@
       <c r="E26" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1506,7 +1546,11 @@
       <c r="E27" s="10" t="n">
         <v>613</v>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
           <t>tak</t>
@@ -1545,7 +1589,11 @@
       <c r="E28" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
           <t>tak</t>
